--- a/OUT_EXCEL/out_3.xlsx
+++ b/OUT_EXCEL/out_3.xlsx
@@ -455,27 +455,19 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TAISAN</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Ma so</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Thuyet</t>
-        </is>
-      </c>
+          <t>TÀI SẢN</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>so cuoi nam</t>
+          <t>Số cuối năm</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>so dau nam</t>
+          <t>Số đầu năm</t>
         </is>
       </c>
     </row>
@@ -505,7 +497,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TAI SAN NGAN HAN</t>
+          <t>TÀI SẢN NGẮN HẠN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -531,12 +523,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>I.</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tien va cac khoan tuong duong tien</t>
+          <t>Tiền và các khoản tương đương tíền</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -571,7 +563,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tien</t>
+          <t>Tiền</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -597,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cac khoan tuong duong tien</t>
+          <t>Các khoản tương đương tiền</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -628,12 +620,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>II.</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cac khoan phai thu ngan han</t>
+          <t>Các khoản phải thu ngắn hạn</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -664,7 +656,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Phai thu ngan han cua khach hang</t>
+          <t>Phải thu ngắn hạn của khách hàng</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -694,12 +686,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tra truoc cho ngudi ban ngan han</t>
+          <t>Trả trước cho người bán ngắn hạn</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -734,7 +726,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phai thu ngan han khac</t>
+          <t>Phải thu ngắn hạn khác</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -769,7 +761,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dy phong phai thu ngan han kho doi</t>
+          <t>Dự phòng phải thu ngắn hạn khó đòi</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -799,12 +791,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>III.</t>
+          <t>II.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hang ton kho</t>
+          <t>Hàng tồn kho</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -839,7 +831,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hang ton kho</t>
+          <t>Hàng tồn kho</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -865,12 +857,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Du phong giam gia hang ton kho</t>
+          <t>Dự phòng giảm giá hàng tồn kho</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -881,12 +873,12 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2.448.449.280</t>
+          <t>(2.448.449.280)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4.157.372.617</t>
+          <t>(4.157.372.617)</t>
         </is>
       </c>
     </row>
@@ -901,7 +893,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tai san ngan han khac</t>
+          <t>Tài sản ngắn han khác</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -932,7 +924,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chi phi tra truoc ngan han</t>
+          <t>Chi phí trả trước ngắn hạn</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -962,12 +954,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Thue gia tri gia tang dugc khau tru</t>
+          <t>Thuế giá trị gia tăng được khấu trừ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -998,7 +990,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Thue va cac khoan khac phai thu</t>
+          <t>Thuế và các khoản khác phải thu</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1029,7 +1021,7 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nha nudc</t>
+          <t>Nhà nước</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1048,7 +1040,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TAISAN DAIHAN</t>
+          <t>TÀI SẢN DÀl HẠN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1074,12 +1066,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>I.</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cac khoan phai thu dai han</t>
+          <t>Các khoản phải thu dài hạn</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1110,7 +1102,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Phai thu dai han khac</t>
+          <t>Phải thu dài hạn khác</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1140,12 +1132,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>II.</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tai san co dinh</t>
+          <t>Tài sản cố định</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1176,7 +1168,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tai san co dinh huu hinh</t>
+          <t>Tài sản cố định hữu hình</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1207,7 +1199,7 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-Nguyen gia</t>
+          <t>-Nguyên giá</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1234,7 +1226,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-Gia trj hao mon luy ke</t>
+          <t>-Giá trị hao mòn lũy kế</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1265,7 +1257,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tai san co dinh thue tai chinh</t>
+          <t>Tài sản cố định thuê tài chính</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1296,7 +1288,7 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-Nguyen gia</t>
+          <t>-Nguyên giá</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1323,7 +1315,7 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-Gia trj hao mon luy ke</t>
+          <t>-Giá trị hao mòn lũy kế</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1334,7 +1326,7 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>(4.395.365.281</t>
+          <t>(4.395.365.281)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1354,7 +1346,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tai san co dinh vo hinh</t>
+          <t>Tài sản cố định vô hình</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1385,7 +1377,7 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-Nguyen gia</t>
+          <t>-Nguyên qiá</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1412,7 +1404,7 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>-Gia trj hao mon luy ke</t>
+          <t>-Giá trị hao mòn lũy kế</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1443,7 +1435,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tai san do dang dai han</t>
+          <t>Tài sản dở dang dài hạn</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1478,7 +1470,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chi phi xay dyng co ban do dang</t>
+          <t>Chi phí xâv dưng cơ bản dở dang</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1509,7 +1501,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dau tu tai chinh dai han</t>
+          <t>Đầu tư tài chính dài hạn</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1544,7 +1536,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dau tuvao cong ty lien doanh, lien ket</t>
+          <t>Đầu tư vào công ty liên doanh, liên kết</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1555,7 +1547,7 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>505.000.000.000</t>
+          <t>505.000.00O.00O</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1570,12 +1562,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2.</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dau tu gop von vao don vj khac</t>
+          <t>Đầu tư góp vốn vào đơn vị khác</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1606,7 +1598,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dy phong dau tu tai chinh dai han</t>
+          <t>Dự phòng đầu tư tài chính dài hạn</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1637,7 +1629,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tai san dai han khac</t>
+          <t>Tài sản dài hạn khác</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1668,7 +1660,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chi phi tra truoc dai han</t>
+          <t>Chi phí trả trước dài hạn</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1699,7 +1691,7 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>TONG CONG TAISAN</t>
+          <t>TỔNG CỘNG TÀI SẢN</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1726,7 +1718,7 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>(270=100+200</t>
+          <t>(270-100+200)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
